--- a/artfynd/A 707-2024 artfynd.xlsx
+++ b/artfynd/A 707-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>117398933</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>117398890</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>117398942</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>117398998</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>117398921</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>117398970</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>117398884</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>117398930</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>117398965</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>117398943</v>
       </c>
       <c r="B19" t="n">
-        <v>57287</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 707-2024 artfynd.xlsx
+++ b/artfynd/A 707-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>117398933</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>117398890</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>117398942</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>117398998</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>117398921</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>117398970</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>117398884</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>117398930</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>117398965</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>117398943</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 707-2024 artfynd.xlsx
+++ b/artfynd/A 707-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>117393201</v>
       </c>
       <c r="B2" t="n">
-        <v>78514</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öradtjärnsbäcken (Öradtjärnsbäcken), Dlr</t>
+          <t>Öradtjärnsbäcken, Öradtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117398933</v>
+        <v>117398910</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,31 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481068</v>
+        <v>481063</v>
       </c>
       <c r="R3" t="n">
-        <v>6811580</v>
+        <v>6811658</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117398901</v>
+        <v>117398928</v>
       </c>
       <c r="B4" t="n">
-        <v>78562</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481082</v>
+        <v>481099</v>
       </c>
       <c r="R4" t="n">
-        <v>6811658</v>
+        <v>6811590</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117398890</v>
+        <v>117398938</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,31 +995,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481082</v>
+        <v>481087</v>
       </c>
       <c r="R5" t="n">
-        <v>6811658</v>
+        <v>6811513</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,6 +1066,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,15 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117393225</v>
+        <v>117398901</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,34 +1096,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öradtjärnsbäcken (Öradtjärnsbäcken), Dlr</t>
+          <t>Öster Korpimäki naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481143</v>
+        <v>481082</v>
       </c>
       <c r="R6" t="n">
-        <v>6811421</v>
+        <v>6811658</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,27 +1156,18 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,26 +1179,21 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117398995</v>
+        <v>117393225</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1259,19 +1215,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öster Korpimäki naturreservat, Dlr</t>
+          <t>Öradtjärnsbäcken, Öradtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481112</v>
+        <v>481143</v>
       </c>
       <c r="R7" t="n">
-        <v>6811414</v>
+        <v>6811421</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1301,18 +1254,27 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1324,65 +1286,52 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117398942</v>
+        <v>117393258</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster Korpimäki naturreservat, Dlr</t>
+          <t>Öradtjärnsbäcken, Öradtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481076</v>
+        <v>481112</v>
       </c>
       <c r="R8" t="n">
-        <v>6811513</v>
+        <v>6811428</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,9 +1361,19 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,47 +1400,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117398998</v>
+        <v>117398978</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1492,7 +1441,7 @@
         <v>481112</v>
       </c>
       <c r="R9" t="n">
-        <v>6811414</v>
+        <v>6811436</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,6 +1482,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,19 +1501,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117393258</v>
+        <v>117398995</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1585,16 +1530,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öradtjärnsbäcken (Öradtjärnsbäcken), Dlr</t>
+          <t>Öster Korpimäki naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>481112</v>
       </c>
       <c r="R10" t="n">
-        <v>6811428</v>
+        <v>6811414</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1624,27 +1572,18 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1663,15 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117398910</v>
+        <v>117398884</v>
       </c>
       <c r="B11" t="n">
-        <v>78514</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,26 +1613,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481063</v>
+        <v>481095</v>
       </c>
       <c r="R11" t="n">
-        <v>6811658</v>
+        <v>6811668</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1750,7 +1689,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,15 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117398921</v>
+        <v>117398890</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481099</v>
+        <v>481082</v>
       </c>
       <c r="R12" t="n">
-        <v>6811638</v>
+        <v>6811658</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,15 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117398970</v>
+        <v>117398921</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481091</v>
+        <v>481099</v>
       </c>
       <c r="R13" t="n">
-        <v>6811440</v>
+        <v>6811638</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1989,15 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117398884</v>
+        <v>117398930</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481095</v>
+        <v>481099</v>
       </c>
       <c r="R14" t="n">
-        <v>6811668</v>
+        <v>6811590</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2099,15 +2022,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117398938</v>
+        <v>117398933</v>
       </c>
       <c r="B15" t="n">
-        <v>86816</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,26 +2033,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2142,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481087</v>
+        <v>481068</v>
       </c>
       <c r="R15" t="n">
-        <v>6811513</v>
+        <v>6811580</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2186,7 +2109,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2205,15 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117398930</v>
+        <v>117398936</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481099</v>
+        <v>481076</v>
       </c>
       <c r="R16" t="n">
-        <v>6811590</v>
+        <v>6811513</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2315,15 +2232,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117398978</v>
+        <v>117398943</v>
       </c>
       <c r="B17" t="n">
-        <v>78480</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,26 +2243,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2358,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481112</v>
+        <v>481070</v>
       </c>
       <c r="R17" t="n">
-        <v>6811436</v>
+        <v>6811518</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2402,7 +2319,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2424,12 +2340,7 @@
         <v>117398965</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,15 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117398943</v>
+        <v>117398970</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481070</v>
+        <v>481091</v>
       </c>
       <c r="R19" t="n">
-        <v>6811518</v>
+        <v>6811440</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2641,15 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117399006</v>
+        <v>117398998</v>
       </c>
       <c r="B20" t="n">
-        <v>57768</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,33 +2558,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2693,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481086</v>
+        <v>481112</v>
       </c>
       <c r="R20" t="n">
-        <v>6811405</v>
+        <v>6811414</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2755,42 +2652,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117398928</v>
+        <v>117399006</v>
       </c>
       <c r="B21" t="n">
-        <v>78514</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2798,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481099</v>
+        <v>481086</v>
       </c>
       <c r="R21" t="n">
-        <v>6811590</v>
+        <v>6811405</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2842,7 +2743,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2861,15 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117398992</v>
+        <v>117398956</v>
       </c>
       <c r="B22" t="n">
-        <v>90517</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,21 +2772,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>260591</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481112</v>
+        <v>481074</v>
       </c>
       <c r="R22" t="n">
-        <v>6811414</v>
+        <v>6811473</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 707-2024 artfynd.xlsx
+++ b/artfynd/A 707-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117393201</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398910</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398928</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398938</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398901</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117393225</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117393258</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398978</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398995</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1704,6 +1754,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398884</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398890</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398921</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398930</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398933</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2229,6 +2304,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398936</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2334,6 +2414,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398943</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2439,6 +2524,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398965</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2544,6 +2634,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398970</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2649,6 +2744,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398998</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2758,6 +2858,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117399006</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2859,8 +2964,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398956</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>